--- a/Fanincial Account/Merchandising Operations.xlsx
+++ b/Fanincial Account/Merchandising Operations.xlsx
@@ -535,6 +535,16 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -548,16 +558,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -914,12 +914,12 @@
       <c r="F2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="45" t="s">
+      <c r="G2" s="39"/>
+      <c r="H2" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="46"/>
-      <c r="J2" s="47"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="42"/>
     </row>
     <row r="3" spans="2:62" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="8" t="s">
@@ -947,64 +947,64 @@
       <c r="J3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="43" t="s">
+      <c r="O3" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="43"/>
-      <c r="AD3" s="43"/>
-      <c r="AE3" s="43"/>
-      <c r="AF3" s="43"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
+      <c r="V3" s="47"/>
+      <c r="W3" s="47"/>
+      <c r="X3" s="47"/>
+      <c r="Y3" s="47"/>
+      <c r="Z3" s="47"/>
+      <c r="AA3" s="47"/>
+      <c r="AB3" s="47"/>
+      <c r="AC3" s="47"/>
+      <c r="AD3" s="47"/>
+      <c r="AE3" s="47"/>
+      <c r="AF3" s="47"/>
+      <c r="AG3" s="47"/>
+      <c r="AH3" s="47"/>
       <c r="AI3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="43" t="s">
+      <c r="AJ3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="43"/>
+      <c r="AK3" s="47"/>
+      <c r="AL3" s="47"/>
+      <c r="AM3" s="47"/>
+      <c r="AN3" s="47"/>
+      <c r="AO3" s="47"/>
       <c r="AP3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="AQ3" s="43" t="s">
+      <c r="AQ3" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AR3" s="43"/>
-      <c r="AS3" s="43"/>
-      <c r="AT3" s="43"/>
-      <c r="AU3" s="43"/>
-      <c r="AV3" s="43"/>
-      <c r="AW3" s="43"/>
-      <c r="AX3" s="43"/>
-      <c r="AY3" s="43"/>
-      <c r="AZ3" s="43"/>
-      <c r="BA3" s="43"/>
-      <c r="BB3" s="43"/>
-      <c r="BC3" s="43"/>
-      <c r="BD3" s="43"/>
-      <c r="BE3" s="43"/>
-      <c r="BF3" s="43"/>
-      <c r="BG3" s="43"/>
-      <c r="BH3" s="43"/>
-      <c r="BI3" s="43"/>
-      <c r="BJ3" s="43"/>
+      <c r="AR3" s="47"/>
+      <c r="AS3" s="47"/>
+      <c r="AT3" s="47"/>
+      <c r="AU3" s="47"/>
+      <c r="AV3" s="47"/>
+      <c r="AW3" s="47"/>
+      <c r="AX3" s="47"/>
+      <c r="AY3" s="47"/>
+      <c r="AZ3" s="47"/>
+      <c r="BA3" s="47"/>
+      <c r="BB3" s="47"/>
+      <c r="BC3" s="47"/>
+      <c r="BD3" s="47"/>
+      <c r="BE3" s="47"/>
+      <c r="BF3" s="47"/>
+      <c r="BG3" s="47"/>
+      <c r="BH3" s="47"/>
+      <c r="BI3" s="47"/>
+      <c r="BJ3" s="47"/>
     </row>
     <row r="4" spans="2:62" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
@@ -1051,64 +1051,64 @@
       </c>
       <c r="M5" s="26"/>
       <c r="N5" s="35"/>
-      <c r="O5" s="39" t="s">
+      <c r="O5" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="39"/>
-      <c r="S5" s="39"/>
-      <c r="T5" s="39"/>
-      <c r="V5" s="39" t="s">
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="43"/>
+      <c r="V5" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="W5" s="39"/>
-      <c r="X5" s="39"/>
-      <c r="Y5" s="39"/>
-      <c r="Z5" s="39"/>
-      <c r="AA5" s="39"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="43"/>
+      <c r="Y5" s="43"/>
+      <c r="Z5" s="43"/>
+      <c r="AA5" s="43"/>
       <c r="AB5" s="37"/>
-      <c r="AC5" s="39" t="s">
+      <c r="AC5" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="AD5" s="39"/>
-      <c r="AE5" s="39"/>
-      <c r="AF5" s="39"/>
-      <c r="AG5" s="39"/>
-      <c r="AH5" s="39"/>
+      <c r="AD5" s="43"/>
+      <c r="AE5" s="43"/>
+      <c r="AF5" s="43"/>
+      <c r="AG5" s="43"/>
+      <c r="AH5" s="43"/>
       <c r="AI5" s="19"/>
-      <c r="AJ5" s="39" t="s">
+      <c r="AJ5" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="AK5" s="39"/>
-      <c r="AL5" s="39"/>
-      <c r="AM5" s="39"/>
-      <c r="AN5" s="39"/>
-      <c r="AO5" s="39"/>
-      <c r="AQ5" s="39" t="s">
+      <c r="AK5" s="43"/>
+      <c r="AL5" s="43"/>
+      <c r="AM5" s="43"/>
+      <c r="AN5" s="43"/>
+      <c r="AO5" s="43"/>
+      <c r="AQ5" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="AR5" s="39"/>
-      <c r="AS5" s="39"/>
-      <c r="AT5" s="39"/>
-      <c r="AU5" s="39"/>
-      <c r="AV5" s="39"/>
-      <c r="AX5" s="39" t="s">
+      <c r="AR5" s="43"/>
+      <c r="AS5" s="43"/>
+      <c r="AT5" s="43"/>
+      <c r="AU5" s="43"/>
+      <c r="AV5" s="43"/>
+      <c r="AX5" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="AY5" s="39"/>
-      <c r="AZ5" s="39"/>
-      <c r="BA5" s="39"/>
-      <c r="BB5" s="39"/>
-      <c r="BC5" s="39"/>
-      <c r="BE5" s="39" t="s">
+      <c r="AY5" s="43"/>
+      <c r="AZ5" s="43"/>
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43"/>
+      <c r="BC5" s="43"/>
+      <c r="BE5" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="BF5" s="39"/>
-      <c r="BG5" s="39"/>
-      <c r="BH5" s="39"/>
-      <c r="BI5" s="39"/>
-      <c r="BJ5" s="39"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
+      <c r="BI5" s="43"/>
+      <c r="BJ5" s="43"/>
     </row>
     <row r="6" spans="2:62" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
@@ -1131,64 +1131,64 @@
         <v>-3280</v>
       </c>
       <c r="N6" s="35"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="42"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="45"/>
+      <c r="S6" s="46"/>
       <c r="T6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="V6" s="40"/>
-      <c r="W6" s="41"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="41"/>
-      <c r="Z6" s="42"/>
+      <c r="V6" s="44"/>
+      <c r="W6" s="45"/>
+      <c r="X6" s="45"/>
+      <c r="Y6" s="45"/>
+      <c r="Z6" s="46"/>
       <c r="AA6" s="18" t="s">
         <v>19</v>
       </c>
       <c r="AB6" s="16"/>
-      <c r="AC6" s="40"/>
-      <c r="AD6" s="41"/>
-      <c r="AE6" s="41"/>
-      <c r="AF6" s="41"/>
-      <c r="AG6" s="42"/>
+      <c r="AC6" s="44"/>
+      <c r="AD6" s="45"/>
+      <c r="AE6" s="45"/>
+      <c r="AF6" s="45"/>
+      <c r="AG6" s="46"/>
       <c r="AH6" s="18" t="s">
         <v>19</v>
       </c>
       <c r="AI6" s="16"/>
-      <c r="AJ6" s="40"/>
-      <c r="AK6" s="41"/>
-      <c r="AL6" s="41"/>
-      <c r="AM6" s="41"/>
-      <c r="AN6" s="42"/>
+      <c r="AJ6" s="44"/>
+      <c r="AK6" s="45"/>
+      <c r="AL6" s="45"/>
+      <c r="AM6" s="45"/>
+      <c r="AN6" s="46"/>
       <c r="AO6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="AQ6" s="40"/>
-      <c r="AR6" s="41"/>
-      <c r="AS6" s="41"/>
-      <c r="AT6" s="41"/>
-      <c r="AU6" s="42"/>
+      <c r="AQ6" s="44"/>
+      <c r="AR6" s="45"/>
+      <c r="AS6" s="45"/>
+      <c r="AT6" s="45"/>
+      <c r="AU6" s="46"/>
       <c r="AV6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="AX6" s="40"/>
-      <c r="AY6" s="41"/>
-      <c r="AZ6" s="41"/>
-      <c r="BA6" s="41"/>
-      <c r="BB6" s="42"/>
+      <c r="AX6" s="44"/>
+      <c r="AY6" s="45"/>
+      <c r="AZ6" s="45"/>
+      <c r="BA6" s="45"/>
+      <c r="BB6" s="46"/>
       <c r="BC6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="BE6" s="39" t="s">
+      <c r="BE6" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="BF6" s="39"/>
-      <c r="BG6" s="39"/>
-      <c r="BH6" s="39"/>
-      <c r="BI6" s="39"/>
-      <c r="BJ6" s="39"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
+      <c r="BI6" s="43"/>
+      <c r="BJ6" s="43"/>
     </row>
     <row r="7" spans="2:62" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
@@ -1318,11 +1318,11 @@
       <c r="BC7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="BE7" s="40"/>
-      <c r="BF7" s="41"/>
-      <c r="BG7" s="41"/>
-      <c r="BH7" s="41"/>
-      <c r="BI7" s="42"/>
+      <c r="BE7" s="44"/>
+      <c r="BF7" s="45"/>
+      <c r="BG7" s="45"/>
+      <c r="BH7" s="45"/>
+      <c r="BI7" s="46"/>
       <c r="BJ7" s="18" t="s">
         <v>19</v>
       </c>
@@ -1716,14 +1716,14 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AX13" s="39" t="s">
+      <c r="AX13" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="AY13" s="39"/>
-      <c r="AZ13" s="39"/>
-      <c r="BA13" s="39"/>
-      <c r="BB13" s="39"/>
-      <c r="BC13" s="39"/>
+      <c r="AY13" s="43"/>
+      <c r="AZ13" s="43"/>
+      <c r="BA13" s="43"/>
+      <c r="BB13" s="43"/>
+      <c r="BC13" s="43"/>
     </row>
     <row r="14" spans="2:62" x14ac:dyDescent="0.25">
       <c r="B14" s="3"/>
@@ -1756,11 +1756,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AX14" s="40"/>
-      <c r="AY14" s="41"/>
-      <c r="AZ14" s="41"/>
-      <c r="BA14" s="41"/>
-      <c r="BB14" s="42"/>
+      <c r="AX14" s="44"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
+      <c r="BB14" s="46"/>
       <c r="BC14" s="18" t="s">
         <v>19</v>
       </c>
@@ -1910,14 +1910,14 @@
       <c r="H19" s="35"/>
       <c r="I19" s="35"/>
       <c r="J19" s="35"/>
-      <c r="AX19" s="39" t="s">
+      <c r="AX19" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="AY19" s="39"/>
-      <c r="AZ19" s="39"/>
-      <c r="BA19" s="39"/>
-      <c r="BB19" s="39"/>
-      <c r="BC19" s="39"/>
+      <c r="AY19" s="43"/>
+      <c r="AZ19" s="43"/>
+      <c r="BA19" s="43"/>
+      <c r="BB19" s="43"/>
+      <c r="BC19" s="43"/>
     </row>
     <row r="20" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B20" s="3"/>
@@ -1928,11 +1928,11 @@
       <c r="H20" s="35"/>
       <c r="I20" s="35"/>
       <c r="J20" s="35"/>
-      <c r="AX20" s="40"/>
-      <c r="AY20" s="41"/>
-      <c r="AZ20" s="41"/>
-      <c r="BA20" s="41"/>
-      <c r="BB20" s="42"/>
+      <c r="AX20" s="44"/>
+      <c r="AY20" s="45"/>
+      <c r="AZ20" s="45"/>
+      <c r="BA20" s="45"/>
+      <c r="BB20" s="46"/>
       <c r="BC20" s="18" t="s">
         <v>19</v>
       </c>
@@ -2360,6 +2360,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="BE5:BJ5"/>
+    <mergeCell ref="BE7:BI7"/>
+    <mergeCell ref="O3:AH3"/>
+    <mergeCell ref="AX13:BC13"/>
+    <mergeCell ref="AX14:BB14"/>
+    <mergeCell ref="AX5:BC5"/>
+    <mergeCell ref="AX6:BB6"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="AX19:BC19"/>
     <mergeCell ref="AX20:BB20"/>
@@ -2376,13 +2383,6 @@
     <mergeCell ref="AQ5:AV5"/>
     <mergeCell ref="AC5:AH5"/>
     <mergeCell ref="AC6:AG6"/>
-    <mergeCell ref="O3:AH3"/>
-    <mergeCell ref="AX13:BC13"/>
-    <mergeCell ref="AX14:BB14"/>
-    <mergeCell ref="AX5:BC5"/>
-    <mergeCell ref="AX6:BB6"/>
-    <mergeCell ref="BE5:BJ5"/>
-    <mergeCell ref="BE7:BI7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Fanincial Account/Merchandising Operations.xlsx
+++ b/Fanincial Account/Merchandising Operations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="54">
   <si>
     <t>Assets</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t>Trial Balance</t>
+  </si>
+  <si>
+    <t>Acconts Reacivable</t>
+  </si>
+  <si>
+    <t>Revenue</t>
   </si>
 </sst>
 </file>
@@ -485,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -536,15 +542,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -558,6 +555,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -840,7 +847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:BJ47"/>
+  <dimension ref="B1:BK62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" customWidth="1"/>
@@ -849,62 +856,64 @@
     <col min="4" max="4" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9.140625" style="1"/>
     <col min="7" max="7" width="9.140625" style="22"/>
-    <col min="8" max="8" width="27.7109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.140625" style="22"/>
-    <col min="11" max="11" width="2.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="27" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="3" style="22" customWidth="1"/>
-    <col min="15" max="15" width="5.85546875" style="22" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" style="22" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.85546875" style="22" customWidth="1"/>
-    <col min="18" max="18" width="7.28515625" style="22" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.28515625" style="22" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="1.7109375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="5.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.42578125" style="14" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="3.42578125" style="22" customWidth="1"/>
-    <col min="29" max="29" width="5.140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.42578125" style="22" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.28515625" style="22" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="7.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="16.28515625" style="22" customWidth="1"/>
-    <col min="35" max="35" width="2.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="5.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="9.140625" style="1"/>
-    <col min="41" max="41" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="2.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="5.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="2.28515625" style="1" customWidth="1"/>
-    <col min="50" max="50" width="9.140625" style="1"/>
-    <col min="51" max="51" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="54" width="9.140625" style="1"/>
-    <col min="55" max="55" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="2.42578125" style="1" customWidth="1"/>
-    <col min="57" max="57" width="5.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="61" width="9.140625" style="1"/>
-    <col min="62" max="62" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="16384" width="9.140625" style="1"/>
+    <col min="8" max="8" width="11.5703125" style="22" customWidth="1"/>
+    <col min="9" max="9" width="27.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="27" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3" style="22" customWidth="1"/>
+    <col min="16" max="16" width="5.85546875" style="22" customWidth="1"/>
+    <col min="17" max="17" width="11.42578125" style="22" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.85546875" style="22" customWidth="1"/>
+    <col min="19" max="19" width="7.28515625" style="22" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.28515625" style="22" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="1.7109375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.42578125" style="22" customWidth="1"/>
+    <col min="30" max="30" width="5.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.42578125" style="22" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.28515625" style="22" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="7.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.28515625" style="22" customWidth="1"/>
+    <col min="36" max="36" width="2.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="9.140625" style="1"/>
+    <col min="42" max="42" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="2.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="2.28515625" style="1" customWidth="1"/>
+    <col min="51" max="51" width="9.140625" style="1"/>
+    <col min="52" max="52" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="55" width="9.140625" style="1"/>
+    <col min="56" max="56" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="2.42578125" style="1" customWidth="1"/>
+    <col min="58" max="58" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="62" width="9.140625" style="1"/>
+    <col min="63" max="63" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:62" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:63" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="11"/>
       <c r="C2" s="38" t="s">
         <v>9</v>
@@ -915,13 +924,14 @@
         <v>11</v>
       </c>
       <c r="G2" s="39"/>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="41"/>
-      <c r="J2" s="42"/>
-    </row>
-    <row r="3" spans="2:62" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="48"/>
+    </row>
+    <row r="3" spans="2:63" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
@@ -938,75 +948,76 @@
         <v>7</v>
       </c>
       <c r="G3" s="17"/>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="25"/>
+      <c r="I3" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="47" t="s">
+      <c r="P3" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="W3" s="47"/>
-      <c r="X3" s="47"/>
-      <c r="Y3" s="47"/>
-      <c r="Z3" s="47"/>
-      <c r="AA3" s="47"/>
-      <c r="AB3" s="47"/>
-      <c r="AC3" s="47"/>
-      <c r="AD3" s="47"/>
-      <c r="AE3" s="47"/>
-      <c r="AF3" s="47"/>
-      <c r="AG3" s="47"/>
-      <c r="AH3" s="47"/>
-      <c r="AI3" s="20" t="s">
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="44"/>
+      <c r="U3" s="44"/>
+      <c r="V3" s="44"/>
+      <c r="W3" s="44"/>
+      <c r="X3" s="44"/>
+      <c r="Y3" s="44"/>
+      <c r="Z3" s="44"/>
+      <c r="AA3" s="44"/>
+      <c r="AB3" s="44"/>
+      <c r="AC3" s="44"/>
+      <c r="AD3" s="44"/>
+      <c r="AE3" s="44"/>
+      <c r="AF3" s="44"/>
+      <c r="AG3" s="44"/>
+      <c r="AH3" s="44"/>
+      <c r="AI3" s="44"/>
+      <c r="AJ3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="47" t="s">
+      <c r="AK3" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="AK3" s="47"/>
-      <c r="AL3" s="47"/>
-      <c r="AM3" s="47"/>
-      <c r="AN3" s="47"/>
-      <c r="AO3" s="47"/>
-      <c r="AP3" s="21" t="s">
+      <c r="AL3" s="44"/>
+      <c r="AM3" s="44"/>
+      <c r="AN3" s="44"/>
+      <c r="AO3" s="44"/>
+      <c r="AP3" s="44"/>
+      <c r="AQ3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="AQ3" s="47" t="s">
+      <c r="AR3" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AR3" s="47"/>
-      <c r="AS3" s="47"/>
-      <c r="AT3" s="47"/>
-      <c r="AU3" s="47"/>
-      <c r="AV3" s="47"/>
-      <c r="AW3" s="47"/>
-      <c r="AX3" s="47"/>
-      <c r="AY3" s="47"/>
-      <c r="AZ3" s="47"/>
-      <c r="BA3" s="47"/>
-      <c r="BB3" s="47"/>
-      <c r="BC3" s="47"/>
-      <c r="BD3" s="47"/>
-      <c r="BE3" s="47"/>
-      <c r="BF3" s="47"/>
-      <c r="BG3" s="47"/>
-      <c r="BH3" s="47"/>
-      <c r="BI3" s="47"/>
-      <c r="BJ3" s="47"/>
-    </row>
-    <row r="4" spans="2:62" x14ac:dyDescent="0.25">
+      <c r="AS3" s="44"/>
+      <c r="AT3" s="44"/>
+      <c r="AU3" s="44"/>
+      <c r="AV3" s="44"/>
+      <c r="AW3" s="44"/>
+      <c r="AX3" s="44"/>
+      <c r="AY3" s="44"/>
+      <c r="AZ3" s="44"/>
+      <c r="BA3" s="44"/>
+      <c r="BB3" s="44"/>
+      <c r="BC3" s="44"/>
+      <c r="BD3" s="44"/>
+      <c r="BE3" s="44"/>
+      <c r="BF3" s="44"/>
+      <c r="BG3" s="44"/>
+      <c r="BH3" s="44"/>
+      <c r="BI3" s="44"/>
+      <c r="BJ3" s="44"/>
+      <c r="BK3" s="44"/>
+    </row>
+    <row r="4" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>46146</v>
       </c>
@@ -1019,19 +1030,29 @@
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="35"/>
-      <c r="H4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="V4" s="7"/>
+      <c r="H4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="3">
+        <f>AB15</f>
+        <v>1370</v>
+      </c>
+      <c r="K4" s="27"/>
+      <c r="T4" s="22">
+        <f>F17</f>
+        <v>3430</v>
+      </c>
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
-      <c r="AI4" s="29"/>
-      <c r="AY4" s="22"/>
-    </row>
-    <row r="5" spans="2:62" x14ac:dyDescent="0.25">
+      <c r="Z4" s="7"/>
+      <c r="AJ4" s="29"/>
+      <c r="AZ4" s="22"/>
+    </row>
+    <row r="5" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="1" t="s">
         <v>21</v>
@@ -1042,75 +1063,81 @@
       </c>
       <c r="G5" s="35"/>
       <c r="H5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="L5" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="M5" s="26"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="43" t="s">
+      <c r="I5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="3">
+        <f>AI11</f>
+        <v>3200</v>
+      </c>
+      <c r="K5" s="27"/>
+      <c r="M5" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N5" s="26"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="P5" s="43"/>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="43"/>
-      <c r="S5" s="43"/>
-      <c r="T5" s="43"/>
-      <c r="V5" s="43" t="s">
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="40"/>
+      <c r="U5" s="40"/>
+      <c r="W5" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="W5" s="43"/>
-      <c r="X5" s="43"/>
-      <c r="Y5" s="43"/>
-      <c r="Z5" s="43"/>
-      <c r="AA5" s="43"/>
-      <c r="AB5" s="37"/>
-      <c r="AC5" s="43" t="s">
+      <c r="X5" s="40"/>
+      <c r="Y5" s="40"/>
+      <c r="Z5" s="40"/>
+      <c r="AA5" s="40"/>
+      <c r="AB5" s="40"/>
+      <c r="AC5" s="37"/>
+      <c r="AD5" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="AD5" s="43"/>
-      <c r="AE5" s="43"/>
-      <c r="AF5" s="43"/>
-      <c r="AG5" s="43"/>
-      <c r="AH5" s="43"/>
-      <c r="AI5" s="19"/>
-      <c r="AJ5" s="43" t="s">
+      <c r="AE5" s="40"/>
+      <c r="AF5" s="40"/>
+      <c r="AG5" s="40"/>
+      <c r="AH5" s="40"/>
+      <c r="AI5" s="40"/>
+      <c r="AJ5" s="19"/>
+      <c r="AK5" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="AK5" s="43"/>
-      <c r="AL5" s="43"/>
-      <c r="AM5" s="43"/>
-      <c r="AN5" s="43"/>
-      <c r="AO5" s="43"/>
-      <c r="AQ5" s="43" t="s">
+      <c r="AL5" s="40"/>
+      <c r="AM5" s="40"/>
+      <c r="AN5" s="40"/>
+      <c r="AO5" s="40"/>
+      <c r="AP5" s="40"/>
+      <c r="AR5" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="AR5" s="43"/>
-      <c r="AS5" s="43"/>
-      <c r="AT5" s="43"/>
-      <c r="AU5" s="43"/>
-      <c r="AV5" s="43"/>
-      <c r="AX5" s="43" t="s">
+      <c r="AS5" s="40"/>
+      <c r="AT5" s="40"/>
+      <c r="AU5" s="40"/>
+      <c r="AV5" s="40"/>
+      <c r="AW5" s="40"/>
+      <c r="AY5" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="AY5" s="43"/>
-      <c r="AZ5" s="43"/>
-      <c r="BA5" s="43"/>
-      <c r="BB5" s="43"/>
-      <c r="BC5" s="43"/>
-      <c r="BE5" s="43" t="s">
+      <c r="AZ5" s="40"/>
+      <c r="BA5" s="40"/>
+      <c r="BB5" s="40"/>
+      <c r="BC5" s="40"/>
+      <c r="BD5" s="40"/>
+      <c r="BF5" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="BF5" s="43"/>
-      <c r="BG5" s="43"/>
-      <c r="BH5" s="43"/>
-      <c r="BI5" s="43"/>
-      <c r="BJ5" s="43"/>
-    </row>
-    <row r="6" spans="2:62" x14ac:dyDescent="0.25">
+      <c r="BG5" s="40"/>
+      <c r="BH5" s="40"/>
+      <c r="BI5" s="40"/>
+      <c r="BJ5" s="40"/>
+      <c r="BK5" s="40"/>
+    </row>
+    <row r="6" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
       <c r="C6" s="1" t="s">
         <v>25</v>
@@ -1119,215 +1146,227 @@
       <c r="F6" s="3"/>
       <c r="G6" s="35"/>
       <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="L6" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="3">
+        <f>U9</f>
+        <v>3280</v>
+      </c>
+      <c r="K6" s="27"/>
+      <c r="M6" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="27">
-        <f>T9</f>
-        <v>-3280</v>
-      </c>
-      <c r="N6" s="35"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="46"/>
-      <c r="T6" s="18" t="s">
+      <c r="N6" s="27">
+        <f>U9</f>
+        <v>3280</v>
+      </c>
+      <c r="O6" s="35"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="V6" s="44"/>
-      <c r="W6" s="45"/>
-      <c r="X6" s="45"/>
-      <c r="Y6" s="45"/>
-      <c r="Z6" s="46"/>
-      <c r="AA6" s="18" t="s">
+      <c r="W6" s="41"/>
+      <c r="X6" s="42"/>
+      <c r="Y6" s="42"/>
+      <c r="Z6" s="42"/>
+      <c r="AA6" s="43"/>
+      <c r="AB6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="AB6" s="16"/>
-      <c r="AC6" s="44"/>
-      <c r="AD6" s="45"/>
-      <c r="AE6" s="45"/>
-      <c r="AF6" s="45"/>
-      <c r="AG6" s="46"/>
-      <c r="AH6" s="18" t="s">
+      <c r="AC6" s="16"/>
+      <c r="AD6" s="41"/>
+      <c r="AE6" s="42"/>
+      <c r="AF6" s="42"/>
+      <c r="AG6" s="42"/>
+      <c r="AH6" s="43"/>
+      <c r="AI6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="AI6" s="16"/>
-      <c r="AJ6" s="44"/>
-      <c r="AK6" s="45"/>
-      <c r="AL6" s="45"/>
-      <c r="AM6" s="45"/>
-      <c r="AN6" s="46"/>
-      <c r="AO6" s="18" t="s">
+      <c r="AJ6" s="16"/>
+      <c r="AK6" s="41"/>
+      <c r="AL6" s="42"/>
+      <c r="AM6" s="42"/>
+      <c r="AN6" s="42"/>
+      <c r="AO6" s="43"/>
+      <c r="AP6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="AQ6" s="44"/>
-      <c r="AR6" s="45"/>
-      <c r="AS6" s="45"/>
-      <c r="AT6" s="45"/>
-      <c r="AU6" s="46"/>
-      <c r="AV6" s="18" t="s">
+      <c r="AR6" s="41"/>
+      <c r="AS6" s="42"/>
+      <c r="AT6" s="42"/>
+      <c r="AU6" s="42"/>
+      <c r="AV6" s="43"/>
+      <c r="AW6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="AX6" s="44"/>
-      <c r="AY6" s="45"/>
-      <c r="AZ6" s="45"/>
-      <c r="BA6" s="45"/>
-      <c r="BB6" s="46"/>
-      <c r="BC6" s="18" t="s">
+      <c r="AY6" s="41"/>
+      <c r="AZ6" s="42"/>
+      <c r="BA6" s="42"/>
+      <c r="BB6" s="42"/>
+      <c r="BC6" s="43"/>
+      <c r="BD6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="BE6" s="43" t="s">
+      <c r="BF6" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="BF6" s="43"/>
-      <c r="BG6" s="43"/>
-      <c r="BH6" s="43"/>
-      <c r="BI6" s="43"/>
-      <c r="BJ6" s="43"/>
-    </row>
-    <row r="7" spans="2:62" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BG6" s="40"/>
+      <c r="BH6" s="40"/>
+      <c r="BI6" s="40"/>
+      <c r="BJ6" s="40"/>
+      <c r="BK6" s="40"/>
+    </row>
+    <row r="7" spans="2:63" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="35"/>
       <c r="H7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="J7" s="3"/>
-      <c r="L7" s="23" t="s">
+      <c r="K7" s="27">
+        <f>AP15</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="M7" s="27">
-        <f>AH11</f>
+      <c r="N7" s="27">
+        <f>AI11</f>
         <v>3200</v>
       </c>
-      <c r="N7" s="36"/>
-      <c r="O7" s="25" t="s">
+      <c r="O7" s="36"/>
+      <c r="P7" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="Q7" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="R7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="25" t="s">
+      <c r="S7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="S7" s="25" t="s">
+      <c r="T7" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="T7" s="25" t="s">
+      <c r="U7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="V7" s="15" t="s">
+      <c r="W7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="W7" s="15" t="s">
+      <c r="X7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="X7" s="15" t="s">
+      <c r="Y7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="Y7" s="15" t="s">
+      <c r="Z7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="Z7" s="15" t="s">
+      <c r="AA7" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="AA7" s="15" t="s">
+      <c r="AB7" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="AB7" s="17"/>
-      <c r="AC7" s="25" t="s">
+      <c r="AC7" s="17"/>
+      <c r="AD7" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="AD7" s="25" t="s">
+      <c r="AE7" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="AE7" s="25" t="s">
+      <c r="AF7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="AF7" s="25" t="s">
+      <c r="AG7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="AG7" s="25" t="s">
+      <c r="AH7" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="AH7" s="25" t="s">
+      <c r="AI7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="AI7" s="17"/>
-      <c r="AJ7" s="15" t="s">
+      <c r="AJ7" s="17"/>
+      <c r="AK7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="AK7" s="15" t="s">
+      <c r="AL7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="AL7" s="15" t="s">
+      <c r="AM7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="AM7" s="15" t="s">
+      <c r="AN7" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="AN7" s="15" t="s">
+      <c r="AO7" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="AO7" s="15" t="s">
+      <c r="AP7" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="AQ7" s="25" t="s">
+      <c r="AR7" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="AR7" s="25" t="s">
+      <c r="AS7" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="AS7" s="25" t="s">
+      <c r="AT7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="AT7" s="25" t="s">
+      <c r="AU7" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="AU7" s="25" t="s">
+      <c r="AV7" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="AV7" s="25" t="s">
+      <c r="AW7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="AX7" s="25" t="s">
+      <c r="AY7" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="AY7" s="25" t="s">
+      <c r="AZ7" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="AZ7" s="25" t="s">
+      <c r="BA7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="BA7" s="25" t="s">
+      <c r="BB7" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="BB7" s="25" t="s">
+      <c r="BC7" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="BC7" s="25" t="s">
+      <c r="BD7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="BE7" s="44"/>
-      <c r="BF7" s="45"/>
-      <c r="BG7" s="45"/>
-      <c r="BH7" s="45"/>
-      <c r="BI7" s="46"/>
-      <c r="BJ7" s="18" t="s">
+      <c r="BF7" s="41"/>
+      <c r="BG7" s="42"/>
+      <c r="BH7" s="42"/>
+      <c r="BI7" s="42"/>
+      <c r="BJ7" s="43"/>
+      <c r="BK7" s="18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:62" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B8" s="34">
         <v>46148</v>
       </c>
@@ -1341,98 +1380,104 @@
       <c r="F8" s="3"/>
       <c r="G8" s="35"/>
       <c r="H8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="J8" s="3"/>
-      <c r="L8" s="31" t="s">
+      <c r="K8" s="27">
+        <f>BD9</f>
+        <v>3800</v>
+      </c>
+      <c r="M8" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="M8" s="27">
-        <f>AA15</f>
+      <c r="N8" s="27">
+        <f>AB15</f>
         <v>1370</v>
       </c>
-      <c r="N8" s="35"/>
-      <c r="S8" s="22">
+      <c r="O8" s="35"/>
+      <c r="T8" s="22">
         <f>F9</f>
         <v>150</v>
       </c>
-      <c r="T8" s="22">
-        <f>S8</f>
-        <v>150</v>
-      </c>
-      <c r="V8" s="7"/>
+      <c r="U8" s="22">
+        <f>S8-T8</f>
+        <v>-150</v>
+      </c>
       <c r="W8" s="7"/>
       <c r="X8" s="7"/>
-      <c r="Y8" s="7">
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7">
         <f>E4</f>
         <v>3800</v>
       </c>
-      <c r="AA8" s="1">
-        <f>Y8</f>
+      <c r="AB8" s="1">
+        <f>Z8</f>
         <v>3800</v>
       </c>
-      <c r="AF8" s="22">
+      <c r="AG8" s="22">
         <f>E25</f>
         <v>3800</v>
       </c>
-      <c r="AH8" s="22">
-        <f>AF8</f>
+      <c r="AI8" s="22">
+        <f>AG8</f>
         <v>3800</v>
       </c>
-      <c r="AI8" s="14"/>
-      <c r="AN8" s="1">
+      <c r="AJ8" s="14"/>
+      <c r="AO8" s="1">
         <f>F5</f>
         <v>3800</v>
       </c>
-      <c r="AO8" s="1">
-        <f>AN8</f>
+      <c r="AP8" s="1">
+        <f>AO8</f>
         <v>3800</v>
       </c>
-      <c r="AQ8" s="22"/>
       <c r="AR8" s="22"/>
       <c r="AS8" s="22"/>
       <c r="AT8" s="22"/>
-      <c r="AU8" s="22">
-        <f>AA5</f>
+      <c r="AU8" s="22"/>
+      <c r="AV8" s="22">
+        <f>AB5</f>
         <v>0</v>
       </c>
-      <c r="AV8" s="22">
-        <f>AU8</f>
+      <c r="AW8" s="22">
+        <f>AV8</f>
         <v>0</v>
       </c>
-      <c r="AX8" s="22"/>
       <c r="AY8" s="22"/>
       <c r="AZ8" s="22"/>
       <c r="BA8" s="22"/>
-      <c r="BB8" s="22">
+      <c r="BB8" s="22"/>
+      <c r="BC8" s="22">
         <f>F26</f>
         <v>3800</v>
       </c>
-      <c r="BC8" s="22">
-        <f>BB8</f>
+      <c r="BD8" s="22">
+        <f>BC8</f>
         <v>3800</v>
       </c>
-      <c r="BE8" s="25" t="s">
+      <c r="BF8" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="BF8" s="25" t="s">
+      <c r="BG8" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="BG8" s="25" t="s">
+      <c r="BH8" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="BH8" s="25" t="s">
+      <c r="BI8" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="BI8" s="25" t="s">
+      <c r="BJ8" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="BJ8" s="25" t="s">
+      <c r="BK8" s="25" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:62" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:63" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
       <c r="C9" s="1" t="s">
         <v>27</v>
@@ -1443,89 +1488,95 @@
       </c>
       <c r="G9" s="35"/>
       <c r="H9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="L9" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="3">
+        <f>BK11</f>
+        <v>2310</v>
+      </c>
+      <c r="K9" s="27"/>
+      <c r="M9" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="32">
-        <f>M6+M7+M8</f>
-        <v>1290</v>
-      </c>
-      <c r="N9" s="35"/>
+      <c r="N9" s="32">
+        <f>N6+N7+N8</f>
+        <v>7850</v>
+      </c>
+      <c r="O9" s="35"/>
       <c r="S9" s="22">
-        <f>F17</f>
+        <f>E43</f>
         <v>3430</v>
       </c>
-      <c r="T9" s="22">
-        <f>T8+R9-S9</f>
-        <v>-3280</v>
-      </c>
-      <c r="V9" s="7"/>
+      <c r="U9" s="22">
+        <f>U8+S9-T9</f>
+        <v>3280</v>
+      </c>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
-      <c r="Y9" s="7">
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7">
         <f>E8</f>
         <v>150</v>
       </c>
-      <c r="AA9" s="1">
-        <f>AA8+Y9-Z9</f>
+      <c r="AB9" s="1">
+        <f>AB8+Z9-AA9</f>
         <v>3950</v>
       </c>
-      <c r="AG9" s="22">
+      <c r="AH9" s="22">
         <f>F32</f>
         <v>300</v>
       </c>
-      <c r="AH9" s="22">
-        <f>AH8+AF9-AG9</f>
+      <c r="AI9" s="22">
+        <f>AI8+AG9-AH9</f>
         <v>3500</v>
       </c>
-      <c r="AI9" s="14"/>
-      <c r="AM9" s="1">
+      <c r="AJ9" s="14"/>
+      <c r="AN9" s="1">
         <f>E12</f>
         <v>300</v>
       </c>
-      <c r="AO9" s="1">
-        <f>AO8+AN9-AM9</f>
+      <c r="AP9" s="1">
+        <f>AP8+AO9-AN9</f>
         <v>3500</v>
       </c>
-      <c r="AQ9" s="22"/>
       <c r="AR9" s="22"/>
       <c r="AS9" s="22"/>
       <c r="AT9" s="22"/>
       <c r="AU9" s="22"/>
-      <c r="AV9" s="22">
-        <f>AV8+AU9-AT9</f>
+      <c r="AV9" s="22"/>
+      <c r="AW9" s="22">
+        <f>AW8+AV9-AU9</f>
         <v>0</v>
       </c>
-      <c r="AX9" s="22"/>
       <c r="AY9" s="22"/>
       <c r="AZ9" s="22"/>
       <c r="BA9" s="22"/>
       <c r="BB9" s="22"/>
-      <c r="BC9" s="22">
-        <f>BC8+BB9-BA9</f>
+      <c r="BC9" s="22"/>
+      <c r="BD9" s="22">
+        <f>BD8+BC9-BB9</f>
         <v>3800</v>
       </c>
-      <c r="BE9" s="22"/>
       <c r="BF9" s="22"/>
       <c r="BG9" s="22"/>
-      <c r="BH9" s="22">
+      <c r="BH9" s="22"/>
+      <c r="BI9" s="22">
         <f>E28</f>
         <v>2400</v>
       </c>
-      <c r="BI9" s="22">
-        <f>AO5</f>
+      <c r="BJ9" s="22">
+        <f>AP5</f>
         <v>0</v>
       </c>
-      <c r="BJ9" s="22">
-        <f>BH9</f>
+      <c r="BK9" s="22">
+        <f>BI9</f>
         <v>2400</v>
       </c>
     </row>
-    <row r="10" spans="2:62" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -1535,106 +1586,122 @@
       <c r="F10" s="3"/>
       <c r="G10" s="35"/>
       <c r="H10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="J10" s="3"/>
-      <c r="L10" s="28" t="s">
+      <c r="K10" s="27">
+        <f>BD17</f>
+        <v>600</v>
+      </c>
+      <c r="M10" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="35"/>
+      <c r="N10" s="27"/>
       <c r="O10" s="35"/>
       <c r="P10" s="35"/>
       <c r="Q10" s="35"/>
       <c r="R10" s="35"/>
       <c r="S10" s="35"/>
       <c r="T10" s="35"/>
-      <c r="U10" s="7"/>
-      <c r="Z10" s="1">
+      <c r="U10" s="35"/>
+      <c r="V10" s="7"/>
+      <c r="AA10" s="1">
         <f>F13</f>
         <v>300</v>
       </c>
-      <c r="AA10" s="22">
-        <f t="shared" ref="AA10:AA15" si="0">AA9+Y10-Z10</f>
+      <c r="AB10" s="22">
+        <f t="shared" ref="AB10:AB15" si="0">AB9+Z10-AA10</f>
         <v>3650</v>
       </c>
-      <c r="AG10" s="22">
+      <c r="AH10" s="22">
         <f>F38</f>
         <v>300</v>
       </c>
-      <c r="AH10" s="22">
-        <f t="shared" ref="AH10:AH11" si="1">AH9+AF10-AG10</f>
+      <c r="AI10" s="22">
+        <f t="shared" ref="AI10:AI11" si="1">AI9+AG10-AH10</f>
         <v>3200</v>
       </c>
-      <c r="AM10" s="1">
+      <c r="AN10" s="1">
         <f>E16</f>
         <v>3500</v>
       </c>
-      <c r="AO10" s="22">
-        <f t="shared" ref="AO10:AO14" si="2">AO9+AN10-AM10</f>
+      <c r="AP10" s="22">
+        <f t="shared" ref="AP10:AP14" si="2">AP9+AO10-AN10</f>
         <v>0</v>
       </c>
-      <c r="BE10" s="22"/>
       <c r="BF10" s="22"/>
       <c r="BG10" s="22"/>
-      <c r="BH10" s="22">
+      <c r="BH10" s="22"/>
+      <c r="BI10" s="22">
         <f>F35</f>
         <v>140</v>
       </c>
-      <c r="BI10" s="22"/>
-      <c r="BJ10" s="22">
-        <f>BJ9+BI10-BH10</f>
+      <c r="BJ10" s="22"/>
+      <c r="BK10" s="22">
+        <f>BK9+BJ10-BI10</f>
         <v>2260</v>
       </c>
     </row>
-    <row r="11" spans="2:62" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="35"/>
-      <c r="H11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="L11" s="31" t="s">
+      <c r="H11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="5"/>
+      <c r="K11" s="45">
+        <f>BD23</f>
+        <v>70</v>
+      </c>
+      <c r="M11" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="27">
-        <f>AO15</f>
+      <c r="N11" s="27">
+        <f>AP15</f>
         <v>0</v>
       </c>
-      <c r="N11" s="35"/>
       <c r="O11" s="35"/>
       <c r="P11" s="35"/>
       <c r="Q11" s="35"/>
       <c r="R11" s="35"/>
       <c r="S11" s="35"/>
       <c r="T11" s="35"/>
-      <c r="U11" s="7"/>
-      <c r="Z11" s="1">
+      <c r="U11" s="35"/>
+      <c r="V11" s="7"/>
+      <c r="AA11" s="1">
         <f>F18</f>
         <v>70</v>
       </c>
-      <c r="AA11" s="22">
+      <c r="AB11" s="22">
         <f t="shared" si="0"/>
         <v>3580</v>
       </c>
-      <c r="AH11" s="22">
+      <c r="AI11" s="22">
         <f t="shared" si="1"/>
         <v>3200</v>
       </c>
-      <c r="AO11" s="22">
+      <c r="AP11" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BI11" s="1">
+      <c r="BJ11" s="1">
         <f>F41</f>
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="2:62" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BK11" s="22">
+        <f>BK10+BJ11-BI11</f>
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="12" spans="2:63" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B12" s="34">
         <v>46150</v>
       </c>
@@ -1647,40 +1714,35 @@
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="35"/>
-      <c r="H12" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="L12" s="23" t="s">
+      <c r="M12" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="M12" s="27">
-        <f>M11</f>
+      <c r="N12" s="27">
+        <f>N11</f>
         <v>0</v>
       </c>
-      <c r="N12" s="36"/>
       <c r="O12" s="36"/>
       <c r="P12" s="36"/>
       <c r="Q12" s="36"/>
       <c r="R12" s="36"/>
       <c r="S12" s="36"/>
       <c r="T12" s="36"/>
-      <c r="U12" s="7"/>
-      <c r="Z12" s="1">
+      <c r="U12" s="36"/>
+      <c r="V12" s="7"/>
+      <c r="AA12" s="1">
         <f>F29</f>
         <v>2400</v>
       </c>
-      <c r="AA12" s="22">
+      <c r="AB12" s="22">
         <f t="shared" si="0"/>
         <v>1180</v>
       </c>
-      <c r="AO12" s="22">
+      <c r="AP12" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:62" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
       <c r="C13" s="1" t="s">
         <v>21</v>
@@ -1691,41 +1753,33 @@
       </c>
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
-      <c r="I13" s="35">
-        <f>SUM(I4:I12)</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="35">
-        <f>SUM(J4:J12)</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="28" t="s">
+      <c r="M13" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="M13" s="27"/>
-      <c r="U13" s="7"/>
-      <c r="Y13" s="1">
+      <c r="N13" s="27"/>
+      <c r="V13" s="7"/>
+      <c r="Z13" s="1">
         <f>E34</f>
         <v>140</v>
       </c>
-      <c r="AA13" s="22">
+      <c r="AB13" s="22">
         <f t="shared" si="0"/>
         <v>1320</v>
       </c>
-      <c r="AO13" s="22">
+      <c r="AP13" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AX13" s="43" t="s">
+      <c r="AY13" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="AY13" s="43"/>
-      <c r="AZ13" s="43"/>
-      <c r="BA13" s="43"/>
-      <c r="BB13" s="43"/>
-      <c r="BC13" s="43"/>
-    </row>
-    <row r="14" spans="2:62" x14ac:dyDescent="0.25">
+      <c r="AZ13" s="40"/>
+      <c r="BA13" s="40"/>
+      <c r="BB13" s="40"/>
+      <c r="BC13" s="40"/>
+      <c r="BD13" s="40"/>
+    </row>
+    <row r="14" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B14" s="3"/>
       <c r="C14" s="1" t="s">
         <v>31</v>
@@ -1734,81 +1788,77 @@
       <c r="F14" s="3"/>
       <c r="G14" s="35"/>
       <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="L14" s="23" t="s">
+      <c r="M14" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="M14" s="27">
-        <f>BC9</f>
+      <c r="N14" s="27">
+        <f>BD9</f>
         <v>3800</v>
       </c>
-      <c r="U14" s="7"/>
-      <c r="Y14" s="1">
+      <c r="V14" s="7"/>
+      <c r="Z14" s="1">
         <f>E40</f>
         <v>50</v>
       </c>
-      <c r="AA14" s="22">
+      <c r="AB14" s="22">
         <f t="shared" si="0"/>
         <v>1370</v>
       </c>
-      <c r="AO14" s="22">
+      <c r="AP14" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AX14" s="44"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
-      <c r="BB14" s="46"/>
-      <c r="BC14" s="18" t="s">
+      <c r="AY14" s="41"/>
+      <c r="AZ14" s="42"/>
+      <c r="BA14" s="42"/>
+      <c r="BB14" s="42"/>
+      <c r="BC14" s="43"/>
+      <c r="BD14" s="18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="2:62" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B15" s="3"/>
       <c r="D15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="L15" s="23" t="s">
+      <c r="M15" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="M15" s="27">
-        <f>BC17</f>
+      <c r="N15" s="27">
+        <f>BD17</f>
         <v>600</v>
       </c>
-      <c r="U15" s="7"/>
-      <c r="AA15" s="22">
+      <c r="V15" s="7"/>
+      <c r="AB15" s="22">
         <f t="shared" si="0"/>
         <v>1370</v>
       </c>
-      <c r="AO15" s="22">
-        <f>AO14+AN15-AM15</f>
+      <c r="AP15" s="22">
+        <f>AP14+AO15-AN15</f>
         <v>0</v>
       </c>
-      <c r="AX15" s="25" t="s">
+      <c r="AY15" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="AY15" s="25" t="s">
+      <c r="AZ15" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="AZ15" s="25" t="s">
+      <c r="BA15" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="BA15" s="25" t="s">
+      <c r="BB15" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="BB15" s="25" t="s">
+      <c r="BC15" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="BC15" s="25" t="s">
+      <c r="BD15" s="25" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="2:62" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B16" s="34">
         <v>46156</v>
       </c>
@@ -1824,25 +1874,26 @@
       <c r="H16" s="35"/>
       <c r="I16" s="35"/>
       <c r="J16" s="35"/>
-      <c r="L16" s="23" t="s">
+      <c r="K16" s="35"/>
+      <c r="M16" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="M16" s="27"/>
-      <c r="U16" s="7"/>
-      <c r="AX16" s="22"/>
+      <c r="N16" s="27"/>
+      <c r="V16" s="7"/>
       <c r="AY16" s="22"/>
       <c r="AZ16" s="22"/>
       <c r="BA16" s="22"/>
-      <c r="BB16" s="22">
+      <c r="BB16" s="22"/>
+      <c r="BC16" s="22">
         <f>E31</f>
         <v>300</v>
       </c>
-      <c r="BC16" s="22">
-        <f>BB16</f>
+      <c r="BD16" s="22">
+        <f>BC16</f>
         <v>300</v>
       </c>
     </row>
-    <row r="17" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B17" s="3"/>
       <c r="C17" s="1" t="s">
         <v>33</v>
@@ -1855,28 +1906,29 @@
       <c r="H17" s="35"/>
       <c r="I17" s="35"/>
       <c r="J17" s="35"/>
-      <c r="L17" s="23" t="s">
+      <c r="K17" s="35"/>
+      <c r="M17" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="M17" s="27">
-        <f>BJ10</f>
+      <c r="N17" s="27">
+        <f>BK10</f>
         <v>2260</v>
       </c>
-      <c r="U17" s="14"/>
-      <c r="AX17" s="22"/>
+      <c r="V17" s="14"/>
       <c r="AY17" s="22"/>
       <c r="AZ17" s="22"/>
       <c r="BA17" s="22"/>
-      <c r="BB17" s="22">
+      <c r="BB17" s="22"/>
+      <c r="BC17" s="22">
         <f>E37</f>
         <v>300</v>
       </c>
-      <c r="BC17" s="22">
-        <f>BC16+BB17-BA17</f>
+      <c r="BD17" s="22">
+        <f>BD16+BC17-BB17</f>
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="2:55" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:56" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="3"/>
       <c r="C18" s="1" t="s">
         <v>36</v>
@@ -1890,15 +1942,16 @@
       <c r="H18" s="35"/>
       <c r="I18" s="35"/>
       <c r="J18" s="35"/>
-      <c r="L18" s="24" t="s">
+      <c r="K18" s="35"/>
+      <c r="M18" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="M18" s="33">
-        <f>M14-M15-M17</f>
+      <c r="N18" s="33">
+        <f>N14-N15-N17</f>
         <v>940</v>
       </c>
     </row>
-    <row r="19" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B19" s="3"/>
       <c r="C19" s="22" t="s">
         <v>35</v>
@@ -1910,16 +1963,17 @@
       <c r="H19" s="35"/>
       <c r="I19" s="35"/>
       <c r="J19" s="35"/>
-      <c r="AX19" s="43" t="s">
+      <c r="K19" s="35"/>
+      <c r="AY19" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="AY19" s="43"/>
-      <c r="AZ19" s="43"/>
-      <c r="BA19" s="43"/>
-      <c r="BB19" s="43"/>
-      <c r="BC19" s="43"/>
-    </row>
-    <row r="20" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="AZ19" s="40"/>
+      <c r="BA19" s="40"/>
+      <c r="BB19" s="40"/>
+      <c r="BC19" s="40"/>
+      <c r="BD19" s="40"/>
+    </row>
+    <row r="20" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="22"/>
@@ -1928,16 +1982,17 @@
       <c r="H20" s="35"/>
       <c r="I20" s="35"/>
       <c r="J20" s="35"/>
-      <c r="AX20" s="44"/>
-      <c r="AY20" s="45"/>
-      <c r="AZ20" s="45"/>
-      <c r="BA20" s="45"/>
-      <c r="BB20" s="46"/>
-      <c r="BC20" s="18" t="s">
+      <c r="K20" s="35"/>
+      <c r="AY20" s="41"/>
+      <c r="AZ20" s="42"/>
+      <c r="BA20" s="42"/>
+      <c r="BB20" s="42"/>
+      <c r="BC20" s="43"/>
+      <c r="BD20" s="18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B21" s="34">
         <v>46176</v>
       </c>
@@ -1953,26 +2008,27 @@
       <c r="H21" s="35"/>
       <c r="I21" s="35"/>
       <c r="J21" s="35"/>
-      <c r="AX21" s="25" t="s">
+      <c r="K21" s="35"/>
+      <c r="AY21" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="AY21" s="25" t="s">
+      <c r="AZ21" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="AZ21" s="25" t="s">
+      <c r="BA21" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="BA21" s="25" t="s">
+      <c r="BB21" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="BB21" s="25" t="s">
+      <c r="BC21" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="BC21" s="25" t="s">
+      <c r="BD21" s="25" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B22" s="3"/>
       <c r="C22" s="22" t="s">
         <v>33</v>
@@ -1986,20 +2042,21 @@
       <c r="H22" s="35"/>
       <c r="I22" s="35"/>
       <c r="J22" s="35"/>
-      <c r="AX22" s="22"/>
+      <c r="K22" s="35"/>
       <c r="AY22" s="22"/>
       <c r="AZ22" s="22"/>
       <c r="BA22" s="22"/>
-      <c r="BB22" s="22">
-        <f>M16</f>
-        <v>0</v>
-      </c>
+      <c r="BB22" s="22"/>
       <c r="BC22" s="22">
-        <f>BB22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:55" x14ac:dyDescent="0.25">
+        <f>E44</f>
+        <v>70</v>
+      </c>
+      <c r="BD22" s="22">
+        <f>BC22</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B23" s="3"/>
       <c r="C23" s="22" t="s">
         <v>34</v>
@@ -2011,17 +2068,18 @@
       <c r="H23" s="35"/>
       <c r="I23" s="35"/>
       <c r="J23" s="35"/>
-      <c r="AX23" s="22"/>
+      <c r="K23" s="35"/>
       <c r="AY23" s="22"/>
       <c r="AZ23" s="22"/>
       <c r="BA23" s="22"/>
       <c r="BB23" s="22"/>
-      <c r="BC23" s="22">
-        <f>BC22+BB23-BA23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BC23" s="22"/>
+      <c r="BD23" s="22">
+        <f>BD22+BC23-BB23</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B24" s="23"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -2031,8 +2089,9 @@
       <c r="H24" s="35"/>
       <c r="I24" s="35"/>
       <c r="J24" s="35"/>
-    </row>
-    <row r="25" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="K24" s="35"/>
+    </row>
+    <row r="25" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B25" s="34">
         <v>46146</v>
       </c>
@@ -2048,8 +2107,9 @@
       <c r="H25" s="35"/>
       <c r="I25" s="35"/>
       <c r="J25" s="35"/>
-    </row>
-    <row r="26" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="K25" s="35"/>
+    </row>
+    <row r="26" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B26" s="3"/>
       <c r="C26" s="3" t="s">
         <v>38</v>
@@ -2063,8 +2123,9 @@
       <c r="H26" s="35"/>
       <c r="I26" s="35"/>
       <c r="J26" s="35"/>
-    </row>
-    <row r="27" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="K26" s="35"/>
+    </row>
+    <row r="27" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -2074,8 +2135,9 @@
       <c r="H27" s="35"/>
       <c r="I27" s="35"/>
       <c r="J27" s="35"/>
-    </row>
-    <row r="28" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="K27" s="35"/>
+    </row>
+    <row r="28" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B28" s="3">
         <v>4</v>
       </c>
@@ -2091,8 +2153,9 @@
       <c r="H28" s="35"/>
       <c r="I28" s="35"/>
       <c r="J28" s="35"/>
-    </row>
-    <row r="29" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="K28" s="35"/>
+    </row>
+    <row r="29" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
         <v>45</v>
@@ -2106,8 +2169,9 @@
       <c r="H29" s="35"/>
       <c r="I29" s="35"/>
       <c r="J29" s="35"/>
-    </row>
-    <row r="30" spans="2:55" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K29" s="35"/>
+    </row>
+    <row r="30" spans="2:56" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -2117,8 +2181,9 @@
       <c r="H30" s="35"/>
       <c r="I30" s="35"/>
       <c r="J30" s="35"/>
-    </row>
-    <row r="31" spans="2:55" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K30" s="35"/>
+    </row>
+    <row r="31" spans="2:56" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="34">
         <v>46150</v>
       </c>
@@ -2134,8 +2199,9 @@
       <c r="H31" s="35"/>
       <c r="I31" s="35"/>
       <c r="J31" s="35"/>
-    </row>
-    <row r="32" spans="2:55" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K31" s="35"/>
+    </row>
+    <row r="32" spans="2:56" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="3"/>
       <c r="C32" s="3" t="s">
         <v>44</v>
@@ -2149,8 +2215,9 @@
       <c r="H32" s="35"/>
       <c r="I32" s="35"/>
       <c r="J32" s="35"/>
-    </row>
-    <row r="33" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K32" s="35"/>
+    </row>
+    <row r="33" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -2160,8 +2227,9 @@
       <c r="H33" s="35"/>
       <c r="I33" s="35"/>
       <c r="J33" s="35"/>
-    </row>
-    <row r="34" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K33" s="35"/>
+    </row>
+    <row r="34" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="3">
         <v>8</v>
       </c>
@@ -2177,8 +2245,9 @@
       <c r="H34" s="35"/>
       <c r="I34" s="35"/>
       <c r="J34" s="35"/>
-    </row>
-    <row r="35" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K34" s="35"/>
+    </row>
+    <row r="35" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="3"/>
       <c r="C35" s="3" t="s">
         <v>39</v>
@@ -2192,8 +2261,9 @@
       <c r="H35" s="35"/>
       <c r="I35" s="35"/>
       <c r="J35" s="35"/>
-    </row>
-    <row r="36" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K35" s="35"/>
+    </row>
+    <row r="36" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
@@ -2203,8 +2273,9 @@
       <c r="H36" s="35"/>
       <c r="I36" s="35"/>
       <c r="J36" s="35"/>
-    </row>
-    <row r="37" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K36" s="35"/>
+    </row>
+    <row r="37" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="34">
         <v>46150</v>
       </c>
@@ -2220,8 +2291,9 @@
       <c r="H37" s="35"/>
       <c r="I37" s="35"/>
       <c r="J37" s="35"/>
-    </row>
-    <row r="38" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K37" s="35"/>
+    </row>
+    <row r="38" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
         <v>44</v>
@@ -2235,8 +2307,9 @@
       <c r="H38" s="35"/>
       <c r="I38" s="35"/>
       <c r="J38" s="35"/>
-    </row>
-    <row r="39" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K38" s="35"/>
+    </row>
+    <row r="39" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
@@ -2246,8 +2319,9 @@
       <c r="H39" s="35"/>
       <c r="I39" s="35"/>
       <c r="J39" s="35"/>
-    </row>
-    <row r="40" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K39" s="35"/>
+    </row>
+    <row r="40" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="3">
         <v>8</v>
       </c>
@@ -2263,8 +2337,9 @@
       <c r="H40" s="35"/>
       <c r="I40" s="35"/>
       <c r="J40" s="35"/>
-    </row>
-    <row r="41" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K40" s="35"/>
+    </row>
+    <row r="41" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="3"/>
       <c r="C41" s="3" t="s">
         <v>47</v>
@@ -2278,8 +2353,9 @@
       <c r="H41" s="35"/>
       <c r="I41" s="35"/>
       <c r="J41" s="35"/>
-    </row>
-    <row r="42" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K41" s="35"/>
+    </row>
+    <row r="42" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
@@ -2289,8 +2365,9 @@
       <c r="H42" s="35"/>
       <c r="I42" s="35"/>
       <c r="J42" s="35"/>
-    </row>
-    <row r="43" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K42" s="35"/>
+    </row>
+    <row r="43" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="34">
         <v>46156</v>
       </c>
@@ -2306,8 +2383,9 @@
       <c r="H43" s="35"/>
       <c r="I43" s="35"/>
       <c r="J43" s="35"/>
-    </row>
-    <row r="44" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K43" s="35"/>
+    </row>
+    <row r="44" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="3"/>
       <c r="C44" s="3" t="s">
         <v>48</v>
@@ -2321,8 +2399,9 @@
       <c r="H44" s="35"/>
       <c r="I44" s="35"/>
       <c r="J44" s="35"/>
-    </row>
-    <row r="45" spans="2:10" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K44" s="35"/>
+    </row>
+    <row r="45" spans="2:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="3"/>
       <c r="C45" s="3" t="s">
         <v>44</v>
@@ -2336,8 +2415,9 @@
       <c r="H45" s="35"/>
       <c r="I45" s="35"/>
       <c r="J45" s="35"/>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K45" s="35"/>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="5"/>
       <c r="C46" s="6"/>
       <c r="D46" s="5"/>
@@ -2347,8 +2427,9 @@
       <c r="H46" s="35"/>
       <c r="I46" s="35"/>
       <c r="J46" s="35"/>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K46" s="35"/>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="E47" s="1">
         <f>SUM(E4:E46)</f>
         <v>21740</v>
@@ -2358,31 +2439,41 @@
         <v>21740</v>
       </c>
     </row>
+    <row r="61" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+    </row>
+    <row r="62" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C62" s="35"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="35"/>
+    </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="BE5:BJ5"/>
-    <mergeCell ref="BE7:BI7"/>
-    <mergeCell ref="O3:AH3"/>
-    <mergeCell ref="AX13:BC13"/>
-    <mergeCell ref="AX14:BB14"/>
-    <mergeCell ref="AX5:BC5"/>
-    <mergeCell ref="AX6:BB6"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="AX19:BC19"/>
-    <mergeCell ref="AX20:BB20"/>
-    <mergeCell ref="AQ3:BJ3"/>
-    <mergeCell ref="BE6:BJ6"/>
-    <mergeCell ref="O5:T5"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="AQ6:AU6"/>
-    <mergeCell ref="AJ3:AO3"/>
-    <mergeCell ref="V6:Z6"/>
-    <mergeCell ref="AJ5:AO5"/>
-    <mergeCell ref="AJ6:AN6"/>
-    <mergeCell ref="V5:AA5"/>
-    <mergeCell ref="AQ5:AV5"/>
-    <mergeCell ref="AC5:AH5"/>
-    <mergeCell ref="AC6:AG6"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="AY19:BD19"/>
+    <mergeCell ref="AY20:BC20"/>
+    <mergeCell ref="AR3:BK3"/>
+    <mergeCell ref="BF6:BK6"/>
+    <mergeCell ref="P5:U5"/>
+    <mergeCell ref="P6:T6"/>
+    <mergeCell ref="AR6:AV6"/>
+    <mergeCell ref="AK3:AP3"/>
+    <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="AK5:AP5"/>
+    <mergeCell ref="AK6:AO6"/>
+    <mergeCell ref="W5:AB5"/>
+    <mergeCell ref="AR5:AW5"/>
+    <mergeCell ref="AD5:AI5"/>
+    <mergeCell ref="AD6:AH6"/>
+    <mergeCell ref="BF5:BK5"/>
+    <mergeCell ref="BF7:BJ7"/>
+    <mergeCell ref="P3:AI3"/>
+    <mergeCell ref="AY13:BD13"/>
+    <mergeCell ref="AY14:BC14"/>
+    <mergeCell ref="AY5:BD5"/>
+    <mergeCell ref="AY6:BC6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
